--- a/Assets/Excel/TaskInfo.xlsx
+++ b/Assets/Excel/TaskInfo.xlsx
@@ -8,8 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="TaskInfo" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="TaskConditionInfo" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,11 +28,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="32">
   <si>
     <t>f_id</t>
   </si>
   <si>
+    <t>f_taskType</t>
+  </si>
+  <si>
     <t>f_taskName</t>
   </si>
   <si>
@@ -55,16 +57,20 @@
     <t>f_completionConditionId</t>
   </si>
   <si>
+    <t>string</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
-    <t>string</t>
-  </si>
-  <si>
     <t>key</t>
   </si>
   <si>
-    <t>任务唯一ID</t>
+    <t>任务唯一ID。
+任务ID_节点ID</t>
+  </si>
+  <si>
+    <t>任务类型</t>
   </si>
   <si>
     <t>任务名称</t>
@@ -77,7 +83,7 @@
 没有任务奖励</t>
   </si>
   <si>
-    <t>下一任务ID。当前节点任务完成后的下一节点任务。若为-1，则说明该任务已完成；</t>
+    <t>下一节点任务ID。当前节点任务完成后的下一节点任务。若为-1，则说明该任务已完成；</t>
   </si>
   <si>
     <t>前置任务ID。""空字符串，
@@ -91,6 +97,9 @@
     <t>当前任务的完成条件ID</t>
   </si>
   <si>
+    <t>1_1</t>
+  </si>
+  <si>
     <t>始于世界之初</t>
   </si>
   <si>
@@ -100,10 +109,25 @@
     <t>1,2</t>
   </si>
   <si>
+    <t>1_2</t>
+  </si>
+  <si>
     <t>终于世界之末</t>
   </si>
   <si>
     <t>与村民对话两次</t>
+  </si>
+  <si>
+    <t>1_-1</t>
+  </si>
+  <si>
+    <t>f_pro</t>
+  </si>
+  <si>
+    <t>当前条件唯一ID</t>
+  </si>
+  <si>
+    <t>条件最大进度</t>
   </si>
 </sst>
 </file>
@@ -1040,20 +1064,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="7"/>
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5"/>
   <cols>
-    <col min="1" max="1" width="24.1111111111111" customWidth="1"/>
-    <col min="2" max="2" width="31.2222222222222" customWidth="1"/>
-    <col min="3" max="3" width="25.3333333333333" customWidth="1"/>
-    <col min="4" max="4" width="27" customWidth="1"/>
-    <col min="5" max="5" width="33.7777777777778" customWidth="1"/>
-    <col min="6" max="6" width="38.8888888888889" customWidth="1"/>
-    <col min="7" max="7" width="42.7777777777778" customWidth="1"/>
-    <col min="8" max="8" width="25.4444444444444" customWidth="1"/>
+    <col min="1" max="2" width="24.1111111111111" customWidth="1"/>
+    <col min="3" max="3" width="31.2222222222222" customWidth="1"/>
+    <col min="4" max="4" width="25.3333333333333" customWidth="1"/>
+    <col min="5" max="5" width="27" customWidth="1"/>
+    <col min="6" max="6" width="33.7777777777778" customWidth="1"/>
+    <col min="7" max="7" width="38.8888888888889" customWidth="1"/>
+    <col min="8" max="8" width="42.7777777777778" customWidth="1"/>
+    <col min="9" max="9" width="25.4444444444444" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:8">
+    <row r="1" s="1" customFormat="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1078,13 +1102,16 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:8">
+    <row r="2" s="1" customFormat="1" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>9</v>
@@ -1093,7 +1120,7 @@
         <v>9</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>9</v>
@@ -1102,79 +1129,91 @@
         <v>9</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:8">
+    <row r="3" s="1" customFormat="1" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" ht="43.2" spans="1:8">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
+    <row r="4" s="1" customFormat="1" ht="43.2" spans="1:9">
+      <c r="A4" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="D4" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="E4" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="H4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:8">
-      <c r="A5" s="1">
+    <row r="5" s="1" customFormat="1" spans="1:9">
+      <c r="A5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="1">
         <v>1</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="C5" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="1">
-        <v>2</v>
-      </c>
-      <c r="F5" s="1"/>
+        <v>23</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="G5" s="1"/>
-      <c r="H5" s="1">
+      <c r="H5" s="1"/>
+      <c r="I5" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" spans="1:8">
-      <c r="A6" s="1">
-        <v>2</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>22</v>
+    <row r="6" s="1" customFormat="1" spans="1:9">
+      <c r="A6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="1">
+        <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="1">
-        <v>-1</v>
-      </c>
-      <c r="H6" s="1">
+        <v>27</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I6" s="1">
         <v>2</v>
       </c>
     </row>
@@ -1188,21 +1227,60 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
-  <sheetData/>
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="1"/>
+  <cols>
+    <col min="1" max="1" width="16.4444444444444" customWidth="1"/>
+    <col min="2" max="2" width="28.4444444444444" customWidth="1"/>
+    <col min="3" max="3" width="14.2222222222222" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:2">
+      <c r="A2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:2">
+      <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:2">
+      <c r="A4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:2">
+      <c r="A5" s="1">
+        <v>1</v>
+      </c>
+      <c r="B5" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:2">
+      <c r="A6" s="1">
+        <v>2</v>
+      </c>
+      <c r="B6" s="1">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/Assets/Excel/TaskInfo.xlsx
+++ b/Assets/Excel/TaskInfo.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="36">
   <si>
     <t>f_id</t>
   </si>
@@ -119,6 +119,18 @@
   </si>
   <si>
     <t>1_-1</t>
+  </si>
+  <si>
+    <t>2_1</t>
+  </si>
+  <si>
+    <t>与我同行</t>
+  </si>
+  <si>
+    <t>首次召唤忆灵</t>
+  </si>
+  <si>
+    <t>2_-1</t>
   </si>
   <si>
     <t>f_pro</t>
@@ -1064,8 +1076,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5"/>
+  <dimension ref="A1:I7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="6"/>
   <cols>
     <col min="1" max="2" width="24.1111111111111" customWidth="1"/>
     <col min="3" max="3" width="31.2222222222222" customWidth="1"/>
@@ -1215,6 +1227,29 @@
       </c>
       <c r="I6" s="1">
         <v>2</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:9">
+      <c r="A7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="1">
+        <v>2</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="1">
+        <v>1</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I7" s="1">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1240,7 +1275,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" spans="1:2">
@@ -1258,10 +1293,10 @@
     </row>
     <row r="4" s="1" customFormat="1" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:2">

--- a/Assets/Excel/TaskInfo.xlsx
+++ b/Assets/Excel/TaskInfo.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9060"/>
+    <workbookView windowWidth="23040" windowHeight="9060" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="TaskInfo" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="40">
   <si>
     <t>f_id</t>
   </si>
@@ -70,7 +70,9 @@
 任务ID_节点ID</t>
   </si>
   <si>
-    <t>任务类型</t>
+    <t>任务类型
+主线：1
+支线：2</t>
   </si>
   <si>
     <t>任务名称</t>
@@ -94,7 +96,7 @@
 不影响当前任务的完成，可由玩家选择是否完成。""空字符串为没有可选任务</t>
   </si>
   <si>
-    <t>当前任务的完成条件ID</t>
+    <t>当前任务节点的完成条件ID</t>
   </si>
   <si>
     <t>1_1</t>
@@ -103,43 +105,60 @@
     <t>始于世界之初</t>
   </si>
   <si>
-    <t>与风星像的共鸣</t>
+    <t>与村民对话</t>
+  </si>
+  <si>
+    <t>1_2</t>
+  </si>
+  <si>
+    <t>终于世界之末</t>
+  </si>
+  <si>
+    <t>与流浪者对话</t>
   </si>
   <si>
     <t>1,2</t>
   </si>
   <si>
-    <t>1_2</t>
-  </si>
-  <si>
-    <t>终于世界之末</t>
-  </si>
-  <si>
-    <t>与村民对话两次</t>
-  </si>
-  <si>
     <t>1_-1</t>
   </si>
   <si>
     <t>2_1</t>
   </si>
   <si>
-    <t>与我同行</t>
-  </si>
-  <si>
-    <t>首次召唤忆灵</t>
+    <t>清理纠纷</t>
+  </si>
+  <si>
+    <t>用武力教他们做人</t>
   </si>
   <si>
     <t>2_-1</t>
   </si>
   <si>
-    <t>f_pro</t>
+    <t>f_maxPro</t>
+  </si>
+  <si>
+    <t>f_taskContentType</t>
+  </si>
+  <si>
+    <t>f_npcId</t>
   </si>
   <si>
     <t>当前条件唯一ID</t>
   </si>
   <si>
     <t>条件最大进度</t>
+  </si>
+  <si>
+    <t>单前节点的任务内容类型ID
+对话：1
+强制战斗：2
+其它：3
+等等</t>
+  </si>
+  <si>
+    <t>当f_contentPerPro为1时，
+要求对话的NpcId.否则为-1</t>
   </si>
 </sst>
 </file>
@@ -1081,7 +1100,7 @@
   <cols>
     <col min="1" max="2" width="24.1111111111111" customWidth="1"/>
     <col min="3" max="3" width="31.2222222222222" customWidth="1"/>
-    <col min="4" max="4" width="25.3333333333333" customWidth="1"/>
+    <col min="4" max="4" width="29.8888888888889" customWidth="1"/>
     <col min="5" max="5" width="27" customWidth="1"/>
     <col min="6" max="6" width="33.7777777777778" customWidth="1"/>
     <col min="7" max="7" width="38.8888888888889" customWidth="1"/>
@@ -1156,7 +1175,7 @@
       <c r="A4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>13</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -1194,11 +1213,9 @@
       <c r="D5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="1"/>
+      <c r="F5" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
@@ -1208,19 +1225,19 @@
     </row>
     <row r="6" s="1" customFormat="1" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B6" s="1">
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>24</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>28</v>
@@ -1262,57 +1279,103 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="5" outlineLevelCol="1"/>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="6" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="16.4444444444444" customWidth="1"/>
     <col min="2" max="2" width="28.4444444444444" customWidth="1"/>
-    <col min="3" max="3" width="14.2222222222222" customWidth="1"/>
+    <col min="3" max="3" width="27.6666666666667" customWidth="1"/>
+    <col min="4" max="4" width="28.4444444444444" customWidth="1"/>
+    <col min="5" max="5" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:2">
+    <row r="1" s="1" customFormat="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>33</v>
       </c>
+      <c r="C1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:2">
+    <row r="2" s="1" customFormat="1" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="C2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:2">
+    <row r="3" s="1" customFormat="1" spans="1:4">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" spans="1:2">
+    <row r="4" s="1" customFormat="1" ht="72" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>39</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:2">
+    <row r="5" s="1" customFormat="1" spans="1:4">
       <c r="A5" s="1">
         <v>1</v>
       </c>
       <c r="B5" s="1">
         <v>1</v>
       </c>
+      <c r="C5" s="1">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
     </row>
-    <row r="6" s="1" customFormat="1" spans="1:2">
+    <row r="6" s="1" customFormat="1" spans="1:4">
       <c r="A6" s="1">
         <v>2</v>
       </c>
       <c r="B6" s="1">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1">
+        <v>1</v>
+      </c>
+      <c r="D6" s="1">
         <v>2</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:4">
+      <c r="A7" s="1">
+        <v>3</v>
+      </c>
+      <c r="B7" s="1">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1">
+        <v>2</v>
+      </c>
+      <c r="D7" s="1">
+        <v>-1</v>
       </c>
     </row>
   </sheetData>
